--- a/artfynd/A 33677-2026 artfynd.xlsx
+++ b/artfynd/A 33677-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135985429</v>
       </c>
       <c r="B2" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>135985436</v>
       </c>
       <c r="B3" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>135985424</v>
       </c>
       <c r="B18" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
         <v>135985441</v>
       </c>
       <c r="B19" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>135985442</v>
       </c>
       <c r="B20" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>135985427</v>
       </c>
       <c r="B21" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>135985431</v>
       </c>
       <c r="B22" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>135985432</v>
       </c>
       <c r="B23" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>135985434</v>
       </c>
       <c r="B24" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>135985435</v>
       </c>
       <c r="B25" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>135985437</v>
       </c>
       <c r="B26" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>135985433</v>
       </c>
       <c r="B28" t="n">
-        <v>98393</v>
+        <v>98396</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>135985438</v>
       </c>
       <c r="B29" t="n">
-        <v>98393</v>
+        <v>98396</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>135985428</v>
       </c>
       <c r="B30" t="n">
-        <v>87270</v>
+        <v>87272</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 33677-2026 artfynd.xlsx
+++ b/artfynd/A 33677-2026 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>136146808</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>136146809</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>136146804</v>
       </c>
       <c r="B6" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>136146806</v>
       </c>
       <c r="B7" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
